--- a/data/trans_orig/P19C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37383</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60727</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327818</t>
+          <t>328615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346029</t>
+          <t>345818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338869</t>
+          <t>338718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357244</t>
+          <t>357787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674926</t>
+          <t>674945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>699520</t>
+          <t>699263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33069</t>
+          <t>33660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59669</t>
+          <t>61554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>541532</t>
+          <t>541737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>561014</t>
+          <t>561435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514639</t>
+          <t>514048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534225</t>
+          <t>534257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1063820</t>
+          <t>1061935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1091015</t>
+          <t>1091320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26043</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>484982</t>
+          <t>484653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497233</t>
+          <t>497303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577522</t>
+          <t>577149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>593461</t>
+          <t>593507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067496</t>
+          <t>1066443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1088625</t>
+          <t>1087598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>380011</t>
+          <t>380463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>396563</t>
+          <t>396234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>421738</t>
+          <t>421943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434311</t>
+          <t>434014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>808379</t>
+          <t>805987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>827733</t>
+          <t>827782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263368</t>
+          <t>263424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271451</t>
+          <t>271399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304465</t>
+          <t>306023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316114</t>
+          <t>316803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>573818</t>
+          <t>573204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586545</t>
+          <t>586319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196317</t>
+          <t>195592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208036</t>
+          <t>207485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231878</t>
+          <t>232278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243274</t>
+          <t>243184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>433461</t>
+          <t>433381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>448711</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119501</t>
+          <t>119057</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125960</t>
+          <t>125949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>197708</t>
+          <t>197394</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207005</t>
+          <t>207037</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319970</t>
+          <t>319947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>331919</t>
+          <t>331902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117081</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208510</t>
+          <t>205090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2350789</t>
+          <t>2350111</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2388457</t>
+          <t>2387772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2623856</t>
+          <t>2625301</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2663410</t>
+          <t>2663885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4987169</t>
+          <t>4990589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5039610</t>
+          <t>5041611</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24042</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83612</t>
+          <t>82921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332705</t>
+          <t>332189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355134</t>
+          <t>355341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326183</t>
+          <t>326354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348208</t>
+          <t>348352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>667245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697938</t>
+          <t>697941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557941</t>
+          <t>557394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579841</t>
+          <t>579053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513493</t>
+          <t>512184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538238</t>
+          <t>537087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1079281</t>
+          <t>1081737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113018</t>
+          <t>1112986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27579</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50818</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561689</t>
+          <t>561496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>577812</t>
+          <t>577999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627542</t>
+          <t>628117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645691</t>
+          <t>645701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1195286</t>
+          <t>1194628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1218525</t>
+          <t>1219760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522109</t>
+          <t>522877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>537809</t>
+          <t>538193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542306</t>
+          <t>541289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>557823</t>
+          <t>556912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1069910</t>
+          <t>1070283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1093219</t>
+          <t>1092062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346676</t>
+          <t>349146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360243</t>
+          <t>360256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379545</t>
+          <t>379572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388718</t>
+          <t>388775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733350</t>
+          <t>732206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>747823</t>
+          <t>747801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255933</t>
+          <t>255409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288338</t>
+          <t>287401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298701</t>
+          <t>298704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547006</t>
+          <t>547366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560240</t>
+          <t>560152</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174580</t>
+          <t>174289</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183870</t>
+          <t>183879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>291746</t>
+          <t>291146</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>301260</t>
+          <t>301273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470842</t>
+          <t>470919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483801</t>
+          <t>483907</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78057</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117722</t>
+          <t>118212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92956</t>
+          <t>92424</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137195</t>
+          <t>134191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>183513</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240628</t>
+          <t>240083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2796937</t>
+          <t>2796447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2836602</t>
+          <t>2835812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3009126</t>
+          <t>3012130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3053365</t>
+          <t>3053897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5820352</t>
+          <t>5820897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5877467</t>
+          <t>5880663</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30152</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>34833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322688</t>
+          <t>322715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341146</t>
+          <t>340948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314076</t>
+          <t>314630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333386</t>
+          <t>333561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645431</t>
+          <t>643854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671043</t>
+          <t>669937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59633</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465519</t>
+          <t>464678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481796</t>
+          <t>481900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456704</t>
+          <t>457387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478201</t>
+          <t>477781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930164</t>
+          <t>929841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956215</t>
+          <t>956944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528123</t>
+          <t>528487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546331</t>
+          <t>546582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548903</t>
+          <t>549933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>564279</t>
+          <t>564869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1085895</t>
+          <t>1085081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1107915</t>
+          <t>1107738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>25847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36688</t>
+          <t>36644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495801</t>
+          <t>495300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>508431</t>
+          <t>508435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517362</t>
+          <t>519037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>535349</t>
+          <t>535540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1020568</t>
+          <t>1020612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1041139</t>
+          <t>1040906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357322</t>
+          <t>358240</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368852</t>
+          <t>368892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379585</t>
+          <t>381573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392595</t>
+          <t>392675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743686</t>
+          <t>744944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>758963</t>
+          <t>759340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221005</t>
+          <t>220770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229107</t>
+          <t>229220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261947</t>
+          <t>262496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274156</t>
+          <t>274780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488269</t>
+          <t>487581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502225</t>
+          <t>502019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143130</t>
+          <t>142590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216207</t>
+          <t>217343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226606</t>
+          <t>226599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>362406</t>
+          <t>363180</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>373608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>57493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96885</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>123209</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153420</t>
+          <t>152832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205803</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2567448</t>
+          <t>2570581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2604758</t>
+          <t>2606840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2743316</t>
+          <t>2744106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2783271</t>
+          <t>2782650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5325845</t>
+          <t>5320588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5378228</t>
+          <t>5378816</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74918</t>
+          <t>77433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333779</t>
+          <t>327442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>370493</t>
+          <t>370296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261597</t>
+          <t>265070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290415</t>
+          <t>290897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612070</t>
+          <t>609555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>656194</t>
+          <t>655385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38384</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367869</t>
+          <t>368516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390296</t>
+          <t>390629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447990</t>
+          <t>447980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480143</t>
+          <t>478544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>825686</t>
+          <t>828678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>863658</t>
+          <t>863435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494704</t>
+          <t>495739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512628</t>
+          <t>513192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500769</t>
+          <t>500838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516644</t>
+          <t>516167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1002712</t>
+          <t>1003034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026734</t>
+          <t>1025272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31319</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831609</t>
+          <t>831770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855527</t>
+          <t>855005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668147</t>
+          <t>669369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684375</t>
+          <t>685186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1505598</t>
+          <t>1507273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1539103</t>
+          <t>1539356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>29973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532888</t>
+          <t>533037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543145</t>
+          <t>543150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>512664</t>
+          <t>513297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525027</t>
+          <t>524571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050737</t>
+          <t>1051132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1065585</t>
+          <t>1065905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>343035</t>
+          <t>344166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>354551</t>
+          <t>354540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>582324</t>
+          <t>582102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597419</t>
+          <t>596950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>929807</t>
+          <t>930510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950213</t>
+          <t>949285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>264562</t>
+          <t>263972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273376</t>
+          <t>272921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>393116</t>
+          <t>393654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402575</t>
+          <t>402369</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>660677</t>
+          <t>661985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>674204</t>
+          <t>674400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80315</t>
+          <t>78717</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140899</t>
+          <t>138984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>109933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>165198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202167</t>
+          <t>205341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>290346</t>
+          <t>288038</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3213322</t>
+          <t>3215237</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3273906</t>
+          <t>3275504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3410711</t>
+          <t>3413629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3466776</t>
+          <t>3468894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6642702</t>
+          <t>6645010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6730881</t>
+          <t>6727707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328615</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345818</t>
+          <t>346985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338718</t>
+          <t>338537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357787</t>
+          <t>357894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674945</t>
+          <t>674547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>699263</t>
+          <t>699736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>33992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61554</t>
+          <t>60193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>541737</t>
+          <t>541789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>561435</t>
+          <t>561324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514048</t>
+          <t>513437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534257</t>
+          <t>534439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1061935</t>
+          <t>1063296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1091320</t>
+          <t>1090747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>39345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>484653</t>
+          <t>484060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497303</t>
+          <t>498110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577149</t>
+          <t>575649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>593507</t>
+          <t>593261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066443</t>
+          <t>1067152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1087598</t>
+          <t>1088186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>380463</t>
+          <t>380924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>396234</t>
+          <t>396553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>421943</t>
+          <t>421637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434014</t>
+          <t>434050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>805987</t>
+          <t>807699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>827782</t>
+          <t>827988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263424</t>
+          <t>262642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271399</t>
+          <t>271286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306023</t>
+          <t>305629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316803</t>
+          <t>316149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>573204</t>
+          <t>571995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586319</t>
+          <t>586373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195592</t>
+          <t>195949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207485</t>
+          <t>207981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232278</t>
+          <t>232249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243184</t>
+          <t>243284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>433381</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>449273</t>
+          <t>448742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119057</t>
+          <t>119400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125949</t>
+          <t>125962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>197394</t>
+          <t>196640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207037</t>
+          <t>207075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319947</t>
+          <t>320522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>331902</t>
+          <t>331845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66970</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104631</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115636</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205090</t>
+          <t>207455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2350111</t>
+          <t>2351410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2387772</t>
+          <t>2387395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2625301</t>
+          <t>2625899</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2663885</t>
+          <t>2662803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4990589</t>
+          <t>4988224</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5041611</t>
+          <t>5042696</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46987</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>43881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>53111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82921</t>
+          <t>84120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332189</t>
+          <t>332463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355341</t>
+          <t>355207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326354</t>
+          <t>327110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348352</t>
+          <t>347999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667245</t>
+          <t>666046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697941</t>
+          <t>697055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74339</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557394</t>
+          <t>558186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579053</t>
+          <t>579982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512184</t>
+          <t>512925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537087</t>
+          <t>537885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1081737</t>
+          <t>1078989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1112986</t>
+          <t>1112918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>50982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561496</t>
+          <t>561288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>577999</t>
+          <t>578079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>628117</t>
+          <t>629100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645701</t>
+          <t>646088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1194628</t>
+          <t>1195122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1219760</t>
+          <t>1219277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522877</t>
+          <t>521210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538193</t>
+          <t>537384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>541289</t>
+          <t>542178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>556912</t>
+          <t>556949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070283</t>
+          <t>1071212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1092303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>349146</t>
+          <t>348585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>360247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379572</t>
+          <t>379065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388775</t>
+          <t>388686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732206</t>
+          <t>733354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>747801</t>
+          <t>748023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255409</t>
+          <t>256476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>287722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547366</t>
+          <t>547155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560152</t>
+          <t>560178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>174704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183879</t>
+          <t>183863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>291146</t>
+          <t>292260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>301273</t>
+          <t>301260</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470919</t>
+          <t>471147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483907</t>
+          <t>483237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118212</t>
+          <t>119741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>93902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>138327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180317</t>
+          <t>181344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240083</t>
+          <t>239580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2796447</t>
+          <t>2794918</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2835812</t>
+          <t>2835283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3012130</t>
+          <t>3007994</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3053897</t>
+          <t>3052419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5820897</t>
+          <t>5821400</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5880663</t>
+          <t>5879636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>38786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60916</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322715</t>
+          <t>323942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340948</t>
+          <t>341104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314630</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333561</t>
+          <t>333078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643854</t>
+          <t>642924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>669937</t>
+          <t>670469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>27580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32853</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59956</t>
+          <t>61769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464678</t>
+          <t>465498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481900</t>
+          <t>481448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457387</t>
+          <t>458337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>477781</t>
+          <t>478846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>929841</t>
+          <t>928028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956944</t>
+          <t>956437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528487</t>
+          <t>527772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546582</t>
+          <t>546032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549933</t>
+          <t>549592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>564869</t>
+          <t>564715</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1085081</t>
+          <t>1085809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1107738</t>
+          <t>1107873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495300</t>
+          <t>495074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>508435</t>
+          <t>508306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>519037</t>
+          <t>518400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>535540</t>
+          <t>535582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1020612</t>
+          <t>1019242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1040906</t>
+          <t>1040817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358240</t>
+          <t>357511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368892</t>
+          <t>368943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381573</t>
+          <t>381184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392675</t>
+          <t>392660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744944</t>
+          <t>743376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>759340</t>
+          <t>759648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220770</t>
+          <t>220945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229220</t>
+          <t>229223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262496</t>
+          <t>263664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274780</t>
+          <t>274274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487581</t>
+          <t>488176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502019</t>
+          <t>502069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142590</t>
+          <t>143046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217343</t>
+          <t>217198</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226599</t>
+          <t>226589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>363180</t>
+          <t>362925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373608</t>
+          <t>373633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>94876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123209</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>153503</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>208873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2570581</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2606840</t>
+          <t>2604197</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2744106</t>
+          <t>2745850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2782650</t>
+          <t>2784939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5320588</t>
+          <t>5322775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5378816</t>
+          <t>5378145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56005</t>
+          <t>47248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>53079</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31603</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>355936</t>
+          <t>351716</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327442</t>
+          <t>331606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>370296</t>
+          <t>364721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280765</t>
+          <t>317300</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265070</t>
+          <t>299454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290897</t>
+          <t>329045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>636701</t>
+          <t>669015</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609555</t>
+          <t>641895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655385</t>
+          <t>686496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>51670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56299</t>
+          <t>62132</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>46687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73364</t>
+          <t>82800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>382145</t>
+          <t>421601</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368516</t>
+          <t>405605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390629</t>
+          <t>431363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463599</t>
+          <t>444769</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447980</t>
+          <t>430939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478544</t>
+          <t>456131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>845743</t>
+          <t>866370</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>828678</t>
+          <t>845702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>863435</t>
+          <t>881815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28303</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40420</t>
+          <t>43747</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505605</t>
+          <t>581281</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495739</t>
+          <t>569601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513192</t>
+          <t>589167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>583378</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500838</t>
+          <t>574585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516167</t>
+          <t>590862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1015503</t>
+          <t>1164658</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1003034</t>
+          <t>1150816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1025272</t>
+          <t>1175543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>36542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>61032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>843457</t>
+          <t>655105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831770</t>
+          <t>643429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855005</t>
+          <t>663325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677774</t>
+          <t>696862</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669369</t>
+          <t>688468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685186</t>
+          <t>704656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1521231</t>
+          <t>1351966</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507273</t>
+          <t>1339024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1539356</t>
+          <t>1363514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>539339</t>
+          <t>585649</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>533037</t>
+          <t>577957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543150</t>
+          <t>589665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>519953</t>
+          <t>578424</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513297</t>
+          <t>571159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>524571</t>
+          <t>584200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1059292</t>
+          <t>1164074</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051132</t>
+          <t>1154588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1065905</t>
+          <t>1171206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>350382</t>
+          <t>388201</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>344166</t>
+          <t>381477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>354540</t>
+          <t>392713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>589782</t>
+          <t>418170</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>582102</t>
+          <t>412425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596950</t>
+          <t>422130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>940164</t>
+          <t>806371</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>930510</t>
+          <t>797912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>949285</t>
+          <t>812240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>269838</t>
+          <t>296310</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263972</t>
+          <t>289796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272921</t>
+          <t>299813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>398696</t>
+          <t>434435</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>393654</t>
+          <t>428405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402369</t>
+          <t>438882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>668534</t>
+          <t>730746</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>661985</t>
+          <t>722954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>674400</t>
+          <t>736809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78717</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138984</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>127565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165198</t>
+          <t>176936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>235502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288038</t>
+          <t>308107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3246701</t>
+          <t>3279863</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3215237</t>
+          <t>3250082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3275504</t>
+          <t>3304349</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3440469</t>
+          <t>3473337</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3413629</t>
+          <t>3448512</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3468894</t>
+          <t>3497883</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6687170</t>
+          <t>6753199</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6645010</t>
+          <t>6715018</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6727707</t>
+          <t>6787623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
